--- a/Result/profitability/2025.xlsx
+++ b/Result/profitability/2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04999999999999998</v>
+        <v>0.03250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-20.23</v>
+        <v>-12.5875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02999999999999998</v>
+        <v>0.06875000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.76875</v>
+        <v>-10.095</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.91</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08124999999999999</v>
+        <v>-0.06124999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.1575</v>
+        <v>-7.933750000000003</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3412499999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.71875</v>
+        <v>-7.638750000000003</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.275</v>
+        <v>-0.2775</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.52625</v>
+        <v>-7.572500000000002</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.27125</v>
+        <v>-0.26375</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.472500000000002</v>
+        <v>-4.433750000000003</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.415</v>
+        <v>-0.4375</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.456250000000002</v>
+        <v>-6.671250000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3549999999999999</v>
+        <v>-0.355</v>
       </c>
       <c r="N9" t="n">
         <v>-7.373750000000002</v>
@@ -1645,7 +1645,7 @@
         <v>0.47</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3174999999999999</v>
+        <v>-0.3175</v>
       </c>
       <c r="N10" t="n">
         <v>-7.512500000000002</v>
@@ -1772,7 +1772,7 @@
         <v>0.26</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2587499999999999</v>
+        <v>-0.25875</v>
       </c>
       <c r="N11" t="n">
         <v>-7.442500000000003</v>
@@ -1899,7 +1899,7 @@
         <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1812499999999999</v>
+        <v>-0.18125</v>
       </c>
       <c r="N12" t="n">
         <v>-8.426250000000003</v>
@@ -2026,7 +2026,7 @@
         <v>-0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05125000000000005</v>
+        <v>0.05125000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>-0.7537500000000019</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>524</v>
+      </c>
+      <c r="D75" t="n">
+        <v>459</v>
+      </c>
+      <c r="E75" t="n">
+        <v>65</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>51</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.81%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>49</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03499999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-18.9075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3829787234042553</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4376407023863125</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.345238095238095</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.183272193690389</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
